--- a/products/pack2-proposal-toolkit/past-performance-template.xlsx
+++ b/products/pack2-proposal-toolkit/past-performance-template.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -102,8 +102,26 @@
       <color rgb="FF01696F"/>
       <sz val="12"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <sz val="9"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="FF6B7280"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF0D1B2A"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -116,8 +134,13 @@
         <bgColor rgb="FF008080"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0D1B2A"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -140,6 +163,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE5E7EB"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE5E7EB"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE5E7EB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE5E7EB"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -151,7 +188,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -243,6 +280,14 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -252,7 +297,7 @@
     <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
     <cellStyle name="Percent" xfId="5" builtinId="5"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="5">
     <dxf>
       <font>
         <name val="Calibri"/>
@@ -292,6 +337,24 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -541,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:O15"/>
+  <dimension ref="B2:P17"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="3" customWidth="1" style="16" min="1" max="1"/>
@@ -557,9 +620,9 @@
     <col width="22" customWidth="1" style="16" min="13" max="13"/>
     <col width="10" customWidth="1" style="16" min="14" max="14"/>
     <col width="14" customWidth="1" style="16" min="15" max="15"/>
+    <col width="20" customWidth="1" style="17" min="16" max="16"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="19.7" customHeight="1" s="17">
       <c r="B2" s="18" t="inlineStr">
         <is>
@@ -574,7 +637,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="37.5" customHeight="1" s="17">
       <c r="B5" s="20" t="inlineStr">
         <is>
@@ -651,6 +713,11 @@
 Status</t>
         </is>
       </c>
+      <c r="P5" s="31" t="inlineStr">
+        <is>
+          <t>Recency Check</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="72" customHeight="1" s="17">
       <c r="B6" s="21" t="inlineStr">
@@ -723,6 +790,10 @@
           <t>Received Back</t>
         </is>
       </c>
+      <c r="P6" s="32">
+        <f>IF(E6="","",IF(ISERR(VALUE(RIGHT(E6,4))),"check dates",IF(YEAR(TODAY())-VALUE(RIGHT(E6,4))&gt;5,"STALE — over 5 yrs",IF(YEAR(TODAY())-VALUE(RIGHT(E6,4))&gt;3,"AGING — over 3 yrs","Current"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="7" ht="72" customHeight="1" s="17">
       <c r="B7" s="21" t="inlineStr">
@@ -795,6 +866,10 @@
           <t>Received Back</t>
         </is>
       </c>
+      <c r="P7" s="32">
+        <f>IF(E7="","",IF(ISERR(VALUE(RIGHT(E7,4))),"check dates",IF(YEAR(TODAY())-VALUE(RIGHT(E7,4))&gt;5,"STALE — over 5 yrs",IF(YEAR(TODAY())-VALUE(RIGHT(E7,4))&gt;3,"AGING — over 3 yrs","Current"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="8" ht="72" customHeight="1" s="17">
       <c r="B8" s="21" t="inlineStr">
@@ -867,6 +942,10 @@
           <t>Sent to POC</t>
         </is>
       </c>
+      <c r="P8" s="32">
+        <f>IF(E8="","",IF(ISERR(VALUE(RIGHT(E8,4))),"check dates",IF(YEAR(TODAY())-VALUE(RIGHT(E8,4))&gt;5,"STALE — over 5 yrs",IF(YEAR(TODAY())-VALUE(RIGHT(E8,4))&gt;3,"AGING — over 3 yrs","Current"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="9" ht="72" customHeight="1" s="17">
       <c r="B9" s="21" t="inlineStr">
@@ -939,6 +1018,10 @@
           <t>Not Sent</t>
         </is>
       </c>
+      <c r="P9" s="32">
+        <f>IF(E9="","",IF(ISERR(VALUE(RIGHT(E9,4))),"check dates",IF(YEAR(TODAY())-VALUE(RIGHT(E9,4))&gt;5,"STALE — over 5 yrs",IF(YEAR(TODAY())-VALUE(RIGHT(E9,4))&gt;3,"AGING — over 3 yrs","Current"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="10" ht="72" customHeight="1" s="17">
       <c r="B10" s="21" t="inlineStr">
@@ -1010,6 +1093,10 @@
         <is>
           <t>Not Sent</t>
         </is>
+      </c>
+      <c r="P10" s="32">
+        <f>IF(E10="","",IF(ISERR(VALUE(RIGHT(E10,4))),"check dates",IF(YEAR(TODAY())-VALUE(RIGHT(E10,4))&gt;5,"STALE — over 5 yrs",IF(YEAR(TODAY())-VALUE(RIGHT(E10,4))&gt;3,"AGING — over 3 yrs","Current"))))</f>
+        <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="17">
@@ -1027,6 +1114,10 @@
       <c r="M11" s="23" t="n"/>
       <c r="N11" s="23" t="n"/>
       <c r="O11" s="23" t="n"/>
+      <c r="P11" s="32">
+        <f>IF(E11="","",IF(ISERR(VALUE(RIGHT(E11,4))),"check dates",IF(YEAR(TODAY())-VALUE(RIGHT(E11,4))&gt;5,"STALE — over 5 yrs",IF(YEAR(TODAY())-VALUE(RIGHT(E11,4))&gt;3,"AGING — over 3 yrs","Current"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="17">
       <c r="B12" s="23" t="n"/>
@@ -1043,6 +1134,10 @@
       <c r="M12" s="23" t="n"/>
       <c r="N12" s="23" t="n"/>
       <c r="O12" s="23" t="n"/>
+      <c r="P12" s="32">
+        <f>IF(E12="","",IF(ISERR(VALUE(RIGHT(E12,4))),"check dates",IF(YEAR(TODAY())-VALUE(RIGHT(E12,4))&gt;5,"STALE — over 5 yrs",IF(YEAR(TODAY())-VALUE(RIGHT(E12,4))&gt;3,"AGING — over 3 yrs","Current"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="17">
       <c r="B13" s="23" t="n"/>
@@ -1059,6 +1154,10 @@
       <c r="M13" s="23" t="n"/>
       <c r="N13" s="23" t="n"/>
       <c r="O13" s="23" t="n"/>
+      <c r="P13" s="32">
+        <f>IF(E13="","",IF(ISERR(VALUE(RIGHT(E13,4))),"check dates",IF(YEAR(TODAY())-VALUE(RIGHT(E13,4))&gt;5,"STALE — over 5 yrs",IF(YEAR(TODAY())-VALUE(RIGHT(E13,4))&gt;3,"AGING — over 3 yrs","Current"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="17">
       <c r="B14" s="23" t="n"/>
@@ -1075,6 +1174,10 @@
       <c r="M14" s="23" t="n"/>
       <c r="N14" s="23" t="n"/>
       <c r="O14" s="23" t="n"/>
+      <c r="P14" s="32">
+        <f>IF(E14="","",IF(ISERR(VALUE(RIGHT(E14,4))),"check dates",IF(YEAR(TODAY())-VALUE(RIGHT(E14,4))&gt;5,"STALE — over 5 yrs",IF(YEAR(TODAY())-VALUE(RIGHT(E14,4))&gt;3,"AGING — over 3 yrs","Current"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="17">
       <c r="B15" s="23" t="n"/>
@@ -1091,6 +1194,17 @@
       <c r="M15" s="23" t="n"/>
       <c r="N15" s="23" t="n"/>
       <c r="O15" s="23" t="n"/>
+      <c r="P15" s="32">
+        <f>IF(E15="","",IF(ISERR(VALUE(RIGHT(E15,4))),"check dates",IF(YEAR(TODAY())-VALUE(RIGHT(E15,4))&gt;5,"STALE — over 5 yrs",IF(YEAR(TODAY())-VALUE(RIGHT(E15,4))&gt;3,"AGING — over 3 yrs","Current"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="33" t="inlineStr">
+        <is>
+          <t>Recency Check reads the end year from Period of Performance. FAR 15.305 evaluates recent performance — most DoD RFPs define that as within 3 to 5 years. Confirm the window in your Section M before dropping a reference.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1112,6 +1226,14 @@
     </cfRule>
     <cfRule type="cellIs" rank="0" priority="6" equalAverage="0" operator="equal" aboveAverage="0" dxfId="2" text="" percent="0" bottom="0">
       <formula>"Unsatisfactory"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P6:P15">
+    <cfRule type="expression" priority="6" dxfId="3">
+      <formula>LEFT(P6,5)="STALE"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="7" dxfId="4">
+      <formula>LEFT(P6,6)="AGING"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
@@ -1145,7 +1267,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:C48"/>
+  <dimension ref="B2:C48"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="3" customWidth="1" style="16" min="1" max="1"/>
@@ -1153,7 +1275,6 @@
     <col width="70" customWidth="1" style="16" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="19.7" customHeight="1" s="17">
       <c r="B2" s="24" t="inlineStr">
         <is>
@@ -1175,7 +1296,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6" ht="25.5" customHeight="1" s="17">
       <c r="B6" s="26" t="inlineStr">
         <is>
@@ -1279,7 +1399,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16" ht="25.5" customHeight="1" s="17">
       <c r="B16" s="26" t="inlineStr">
         <is>
@@ -1347,7 +1466,6 @@
         </is>
       </c>
     </row>
-    <row r="22"/>
     <row r="23" ht="25.5" customHeight="1" s="17">
       <c r="B23" s="26" t="inlineStr">
         <is>
@@ -1403,7 +1521,6 @@
         </is>
       </c>
     </row>
-    <row r="28"/>
     <row r="29" ht="25.5" customHeight="1" s="17">
       <c r="B29" s="26" t="inlineStr">
         <is>
@@ -1471,7 +1588,6 @@
         </is>
       </c>
     </row>
-    <row r="35"/>
     <row r="36" ht="25.5" customHeight="1" s="17">
       <c r="B36" s="26" t="inlineStr">
         <is>
@@ -1564,7 +1680,6 @@
         </is>
       </c>
     </row>
-    <row r="44"/>
     <row r="45" ht="25.5" customHeight="1" s="17">
       <c r="B45" s="26" t="inlineStr">
         <is>
@@ -1633,14 +1748,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:B46"/>
+  <dimension ref="B2:B49"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="3" customWidth="1" style="16" min="1" max="1"/>
     <col width="90" customWidth="1" style="16" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="19.7" customHeight="1" s="17">
       <c r="B2" s="24" t="inlineStr">
         <is>
@@ -1655,8 +1769,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="21.75" customHeight="1" s="17">
       <c r="B6" s="29" t="inlineStr">
         <is>
@@ -1671,7 +1783,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9" ht="18" customHeight="1" s="17">
       <c r="B9" s="30" t="inlineStr">
         <is>
@@ -1707,7 +1818,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15" ht="21.75" customHeight="1" s="17">
       <c r="B15" s="29" t="inlineStr">
         <is>
@@ -1750,7 +1860,6 @@
         </is>
       </c>
     </row>
-    <row r="21"/>
     <row r="22" ht="21.75" customHeight="1" s="17">
       <c r="B22" s="29" t="inlineStr">
         <is>
@@ -1807,7 +1916,6 @@
         </is>
       </c>
     </row>
-    <row r="30"/>
     <row r="31" ht="21.75" customHeight="1" s="17">
       <c r="B31" s="29" t="inlineStr">
         <is>
@@ -1857,7 +1965,6 @@
         </is>
       </c>
     </row>
-    <row r="38"/>
     <row r="39" ht="21.75" customHeight="1" s="17">
       <c r="B39" s="29" t="inlineStr">
         <is>
@@ -1900,11 +2007,24 @@
         </is>
       </c>
     </row>
-    <row r="45"/>
     <row r="46" ht="18" customHeight="1" s="17">
       <c r="B46" s="30" t="inlineStr">
         <is>
           <t>© Acqlerate — Defense Acquisitions Academy. For training use only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="34" t="inlineStr">
+        <is>
+          <t>License &amp; Use</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="33" t="inlineStr">
+        <is>
+          <t>This template is licensed for use on one program, by one organization, under your Acqlerate purchase. Customize the text, branding, and layout freely for your own program. Deploying it company-wide, sharing it outside your organization, or reselling it requires an Acqlerate Team License (acqlerate.com/team).</t>
         </is>
       </c>
     </row>
